--- a/00-TrainRnns/tau-3/X-otm/BestModels-otm.xlsx
+++ b/00-TrainRnns/tau-3/X-otm/BestModels-otm.xlsx
@@ -477,182 +477,182 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>17</v>
+        <v>380</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>model_arch79_r0.9_Ld0.3_Lp0.7_seed6066</t>
+          <t>model_arch92_r0.9_Ld0.3_Lp0.7_seed9339</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[79]</t>
+          <t>[92]</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.8851408220528537</v>
+        <v>0.8715187436952381</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8932513124954181</v>
+        <v>0.9093064170596028</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8857713261044967</v>
+        <v>0.8989836647208431</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8851408220528537</v>
+        <v>0.8715187436952381</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8932513124954181</v>
+        <v>0.9093064170596028</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8857713261044967</v>
+        <v>0.8989836647208431</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8787227809447925</v>
+        <v>0.88238379977962</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>model_arch79_r0.9_Ld0.3_Lp0.7_seed8998</t>
+          <t>model_arch82_r0.01_Ld0.5_Lp0.5_seed4073</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[79]</t>
+          <t>[82]</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8769911230610875</v>
+        <v>0.8790693194077867</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8146944140197434</v>
+        <v>0.901867764559673</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9078781166003154</v>
+        <v>0.8876876829162701</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8769911230610875</v>
+        <v>0.8790693194077867</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8146944140197434</v>
+        <v>0.901867764559673</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9078781166003154</v>
+        <v>0.8876876829162701</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8531094124181956</v>
+        <v>0.8794949997525621</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>model_arch79_r0.01_Ld0.5_Lp0.5_seed5663</t>
+          <t>model_arch82_r0.01_Ld0.5_Lp0.5_seed9339</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[79]</t>
+          <t>[82]</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.8157079833794127</v>
+        <v>0.8673605673317222</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8540409416047441</v>
+        <v>0.898230466198788</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9227732474077949</v>
+        <v>0.9034278036157452</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8157079833794127</v>
+        <v>0.8673605673317222</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8540409416047441</v>
+        <v>0.898230466198788</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9227732474077949</v>
+        <v>0.9034278036157452</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8501076024101025</v>
+        <v>0.8788265117911478</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>10</v>
+        <v>145</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>model_arch79_r0.01_Ld0.3_Lp0.7_seed8998</t>
+          <t>model_arch84_r0.01_Ld0.7_Lp0.3_seed9339</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[79]</t>
+          <t>[84]</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.8371384522166903</v>
+        <v>0.8870168893061355</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8402136590146904</v>
+        <v>0.9020146077399598</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8705219604470269</v>
+        <v>0.8708513913357329</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8371384522166903</v>
+        <v>0.8870168893061355</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8402136590146904</v>
+        <v>0.9020146077399598</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8705219604470269</v>
+        <v>0.8708513913357329</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8389534013533979</v>
+        <v>0.8762028277199978</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>2</v>
+        <v>298</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>model_arch79_r0.01_Ld0.5_Lp0.5_seed6066</t>
+          <t>model_arch89_r0.9_Ld0.7_Lp0.3_seed2393</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[79]</t>
+          <t>[89]</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8831698175023904</v>
+        <v>0.8929215411721177</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7993731451079712</v>
+        <v>0.9170151508535557</v>
       </c>
       <c r="F6" t="n">
-        <v>0.861826102111974</v>
+        <v>0.8512818939876858</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8831698175023904</v>
+        <v>0.8929215411721177</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7993731451079712</v>
+        <v>0.9170151508535557</v>
       </c>
       <c r="I6" t="n">
-        <v>0.861826102111974</v>
+        <v>0.8512818939876858</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8352871370801705</v>
+        <v>0.8748766701827579</v>
       </c>
     </row>
   </sheetData>
